--- a/data/250214_K27me123ac_P2S25p_TAZEEDUTX_cell_counts.xlsx
+++ b/data/250214_K27me123ac_P2S25p_TAZEEDUTX_cell_counts.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jgreene3/Library/CloudStorage/GoogleDrive-jgreene@altius.org/My Drive/UW/PhD/K27me2/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684393D6-31E4-134B-9C82-CFBBC3205174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40760" yWindow="1120" windowWidth="40060" windowHeight="22720" xr2:uid="{A329B003-26FE-574A-A6A2-0B03C33B2F2A}"/>
